--- a/channels/유사도별_채널목록.xlsx
+++ b/channels/유사도별_채널목록.xlsx
@@ -8,16 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기준 채널" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="하" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상 (83개)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중 (119개)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="하 (49개)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기준 채널'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'상'!$A$1:$I$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'중'!$A$1:$I$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'하'!$A$1:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'상 (83개)'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'중 (119개)'!$A$1:$I$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'하 (49개)'!$A$1:$I$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -63,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,18 +92,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -477,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -503,88 +501,81 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>· 기준 채널: 세상만사, 사연만남 (2개)</t>
+          <t>· 상 (거의 같음): 세상만사·사연만남 2개 + 시댁 소재 60% 이상이고 1시간 넘는 영상 50% 이상인 채널 81개 = 총 83개</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>· 상 (거의 같음): 시댁 소재 60% 이상 + 1시간 넘는 영상 50% 이상 (81개)</t>
+          <t>· 중 (비슷함): 시댁 소재 40% 이상이지만 영상이 짧거나 다른 사연이 섞임 (119개)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>· 중 (비슷함): 시댁 소재 40% 이상이지만 영상이 짧거나 다른 사연이 섞임 (119개)</t>
+          <t>· 하 (일부만 비슷): 시댁 소재 15~40% (49개)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>· 하 (일부만 비슷): 시댁 소재 15~40% (49개)</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>열 설명</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>열 설명</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>· 채널이름을 누르면 YouTube 채널로 이동합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>· 채널이름을 누르면 YouTube 채널로 이동합니다.</t>
+          <t>· 시댁 소재 비율: 영상 제목에 시모·시누·동서·며느리 등이 들어간 비율</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>· 시댁 소재 비율: 영상 제목에 시모·시누·동서·며느리 등이 들어간 비율</t>
+          <t>· 1시간 이상 영상 비율: 전체 영상 중 1시간 넘는 영상의 비율</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>· 1시간 이상 영상 비율: 전체 영상 중 1시간 넘는 영상의 비율</t>
+          <t>· 최근 30일 업로드: 최근 한 달 동안 올린 영상 수 (0이면 업로드를 멈춘 채널)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>· 최근 30일 업로드: 최근 한 달 동안 올린 영상 수 (0이면 업로드를 멈춘 채널)</t>
+          <t>· 조회수 1위 영상을 누르면 그 영상으로 이동합니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>· 조회수 1위 영상을 누르면 그 영상으로 이동합니다.</t>
+          <t>· 각 시트는 구독자 많은 순서입니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>· 각 시트는 구독자 많은 순서입니다.</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>기준일: 2026-10-29 (쇼츠·라이브 제외)</t>
         </is>
@@ -601,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -665,45 +656,45 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>사연만남 (@사연만남1짱)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+          <t>사연만남 (@사연만남1짱) ★기준</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>3.52만</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1시간 36분</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>72,490</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>병원 근무하는 내가 남편의 암을 알게되고 말해 주려는데  내연녀와 함께 있는 남편을 보게 되고 "이왕 이렇게 걸린거 그냥 이혼하자" 남편놈 인생이 그날로 종쳤습니다</t>
         </is>
@@ -712,3926 +703,3847 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>세상만사</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+          <t>세상만사 ★기준</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>2.27만</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1시간 31분</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>41,360</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>친정엄마 모시고 백화점 갔는데 우연히 마주친 변호사 동서가 비웃네요 "형편도 안되면서 여긴 왜 왔어요?" 그때 동서 옆에 있던 회사 대표가 90도로 인사하자 동서는 쓰러지는데..</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <autoFilter ref="A1:I3"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I82"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>채널이름</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>구독자</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>영상 수</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>시댁 소재 비율</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>1시간 이상 영상 비율</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>평균 길이</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>최근 30일 업로드</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>최근 10개 평균 조회수</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>조회수 1위 영상</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>사연라디오 '썰맘'</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>34.4만</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>903</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2시간 26분</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>반전실화사연-형님 장례후 도망간 만삭의 형수가 10년만에 찾아와 100만원만 빌려달라는데..형수 뒤밟아 도착한곳 문을 연순간 형수를 안고 오열했습니다_사연라디오썰맘/사연읽어주는남녀</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>꽃편지야담</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>10.1만</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1시간 16분</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>340,582</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>돌잔치 2시간 전 100인분 취소한 동서, 무시하던 형님의 진짜 정체를 알고 얼어붙었습니다ㅣ노후사연ㅣ반전사연ㅣ감동사연ㅣ오디오북 l 인생사연ㅣ</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>썰극장</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>7.34만</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>402</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1시간 6분</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>10,670</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>시모 퇴원하는날 시누들 전부 우리집에 불러 나한테 한마디 상의도 없이 시모를 모시겠다는 남편..시누들이 내게 고맙다며 잘 모셔달라고 할때 내가 한마디 하자 풍비박산 나는데</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>사연모아 • 조회수 98만회</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>6.17만</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1시간 54분</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>15,890</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>내가 산 10억 신혼집에 시어머니 짐부터 들인 남편, 시아버지가 몰래 알려준 1702호에 찾아갔다가 경악했습니다</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>인생의 뒷모습</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>5.33만</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>381</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1시간 32분</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>1,964</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>상견례날, 휠체어 탄 아버지를 조롱하고 모욕한 시댁, 500억 시댁회사 공중분해시켰습니다 (고부갈등,오디오북,라디오사연)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>송이의 사연극장</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>5.29만</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1시간 1분</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>15,379</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>남편이 부사장이 되자 사장 딸이랑 재혼할테니 이혼 조건으로 강남 아파트를 준다는 시모 "저야 땡큐죠^^! 감사합니다" 아파트 받고 쿨하게 갈라섰더니 한달 후 시모와 남편 발광하는데</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>호냔썰</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>3.77만</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2시간 12분</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>3,422</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>40억 강남 아파트 해주니까 문전박대하는 며느리 바로 급매로 넘겼습니다 | 고부갈등 | 노후사연 | 인생사연 | 사연 | 노후 | 오디오북 | 시니어드라마</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>노을빛 사연</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>3.29만</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1시간 4분</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>4,092</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>치매 시어머니 5년 모셨어요. 시어머니는 형님들에게 500만원짜리 한복을 주셨지만, 저에게는 낡은 보자기를 던지며, "남은 음식들 싸놨다 가져가라" 집에 와서 보자기를 풀어보니..</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>사연반짝</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2.85만</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>1시간 49분</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>43,650</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>빈털터리로 쫓겨나는 며느리 신나서 만세 부르며 나가는데 / 고부갈등 / 오디오북 /</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>평온한 노년</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2.32만</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2시간 12분</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>37,968</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>며느리가 약을 탄 바나나우유를 건넸다  그리고 5분 뒤 바나나 우유 맛있죠 며느리의 물음에 대답했죠, 그 우유 손주가 먹었는데 그 순간 며느리가 게거품을</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>실화보감</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2.31만</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1시간 14분</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>7,154</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>판사딸인줄 모르고 예비 며느리의 뺨을 때린 시어머니와 조롱하던 시댁식구들, 파산시키고 참교육시켰습니다 | #노후사연 | #사이다사연 | #시니어사연 | #오디오북</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>인생사연들</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2.01만</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1시간 22분</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>3,750</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>남편 죽은지 3일째, 시댁은 조의금을 싹 챙긴 뒤 비오는 밤에 저와 딸을 내쫓았죠. 그날 새벽, 죽은 남편에게 온 문자 한통 “나 살아있어. 여기 주소로 와!”</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>사연다방8</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1.84만</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1시간 10분</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>12,902</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>3일전 이혼한 며느리에게서 전화가 왔습니다 아줌마, 그 집 이제 제 거예요 방 빼세요 | #노후사연 | #사이다사연 | #시니어사연 | #오디오북</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>달빛라디오</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>1.71만</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1시간 3분</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>18,060</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>신혼 첫날 시누이에게 말대꾸했다며 영하17도에 옥탑방에 가둔 남편, 다음날 옥탑방 문을 연 남편은 믿을수 없는 광경에 나자빠지는데</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>박카스인생사연</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>1.54만</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1시간 34분</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>7,020</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>동창회에서 뺨맞고 조롱당하는 시아버지를 우연히 목격한 재벌 며느리, 다음 날 시아버지의 동창들 회사가 줄줄이 개박살나고...|인생사연 |노후사연 | 감동사연 |시니어사연 |</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>따뜻한한페이지</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>1.39만</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>427</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1시간 24분</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>904</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>이혼 1년 후, 재벌회장은 아내가 갓난아기를 업고 고속도로에서 뻥튀기파는 모습을 보고 곧바로 차를 세우는데…ㅣ반전사연ㅣ노후사연ㅣ사연사디오ㅣ오디오북ㅣ고부갈등</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>재벌가의 눈물</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>1.37만</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>3시간 3분</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>42,810</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>친정엄마가 보낸 미역국을 싱크대에 버린 시어머니… 임신한 아내가 맨손으로 줍는 순간 남편이 들어왔다ㅣ노후사연ㅣ감동사연ㅣ오디오북</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>달빛인생TV</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>1.17만</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1시간 12분</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>1,128</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>“부양은 의무라며?” 며느리가 병원비 끊자 지옥문 열린 시어머니! | 오디오북 시니어사연 고부사연</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>인생사연달항아리</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>1.06만</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>1시간 38분</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>54,920</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>가난한 집 딸이라고 나를 내쫓은 시어머니 "내가 4000억 자산 대표인거 몰랐죠?"</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>calimad3111</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>1.06만</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>2시간 14분</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>333</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>4,238</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>첫날부터 손만 잡고 자자는 남편 ＂우리 부부관계는 천천히 하자＂ 모두 잠든 새벽, 시어머니 방문 너머로  남편의 신음소리가 새어나오고 방문을 연 순간 주저앉고 마는데   !</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>사연캠프</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>8.33천</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1시간 24분</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2,650</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>새해첫날 친정에 용돈 보내드렸더니 차려둔 밥상 엎어버린 시어머니 “호로잡년! 시댁 돈을 퍼날라?” 저는 매달 보내던 생활비 끊었습니다 다음날, 기막힌 광경이 펼쳐지는데</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>카를로스 프라임</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>8.05천</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>354</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>2시간 43분</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>341</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>며느리가 약을 탄 바나나우유를 건넸다  그리고 5분 뒤 바나나 우유 맛있죠 며느리의 물음에 대답했죠, 그 우유 손주가 먹었는데 그 순간 며느리가 게거품을</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>사연한권</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>7.5천</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1시간 24분</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>온 몸에 문신한 예비며느리, 하지만 문제는 문신이 아니었습니다.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>사연인생극장</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>6.95천</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>1시간 24분</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>533</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>임신한 내연녀가 내 뺨 때리는데 “언니 이제 똥차 좀 빼줄래요!” 남편과 시모는 웃으며 구경만하길래 저는 시댁 집을 팔고 떠났습니다 며칠 뒤, 시댁은 풍비박산 나는데</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>비밀 이야기들</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>5.37천</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>983</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1시간 31분</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>(실화사연) 6박7일 출장 잡혔다더니 몰래 시부모 데리고 유럽여행 다녀온 남편   당신 곧 퇴직금 받지 미리 대출 받아서 좀 썼어!  남편과 시모에게 참교육하고 이혼합니다</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>가을 이야기</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>4.13천</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1시간 31분</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>(실화사연) 혼인 신고도 안 했는데 내 명의로 된 신혼집에 찾아온 시모가 같이 살자며 짐까지 싸오는데    라디오사연  썰사연 사이다사연 감동사연</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>마음에 남은 인생</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>3.6천</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>2시간 10분</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>12,782</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>어떻게 쫒아내지   우연히 안방에서 아들며드리가 하는말을 듣고 전재산 팔고 계획실행한 할머니  고부갈등 고부사연 감동사연 오디오북 시니어사연 아들며느리 어머니</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>사연한편</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>3.39천</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>2시간 1분</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>남편 빚 10억 갚아주려 은행 간 날 대출금 갚자마자 이혼하라는 시모 “돈 들어왔는데 지가 어쩔건데!” 저는 조용히 은행에 전화했습니다 다음날 시모의 부재중 전화 72통</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>실화 인생사연</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2.88천</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>1시간 8분</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>남편이 강남 건물주가 되자 돈봉투 던져주며 이혼하라는 시모 “거머리년! 너같은년은 널렸다!” 저는 조용히 집을 나왔습니다 다음날 하루종일 걸려오는 시모전화</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>썰을 좋아하는 남자</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2.21천</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>1시간 31분</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>8,533</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>신청사연 시댁 친정 둘다 안가고 명절에 식당 연 남편이 화장실에서 시댁에 간다는 통화소리 배신감에 문 부수고 나가려다 통곡 하는데  감동사연 사이다사연 라디오드라마 사연라디오</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>2011VANIZIA</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2.16천</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1시간 23분</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>뚱뚱해서 버린 전처 비웃으러 동창회에 새로운 아내와 구경 갔다가 경악했습니다 [ 오디오드라마 노후사연 감동사연 시니어사연 오디오북 사연라디오 인생사연 ]</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>가족극장 라디오</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>1.98천</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>1시간 31분</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>391</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>(반전 사연) 시골에서 고속버스 타고 친정엄마가 왔는데 김치만 받고 돌려보낸 남편 ”친정엄마가 전해줄 무언가를 꺼내자 5초 뒤, 남편 얼굴이 썩어버리는데 /사이다사연/라디오드라마</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>라디오 드라마: 실화 사연</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>1.86천</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>1.2천</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>1시간 23분</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>529</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>실화사연  시부 제사에 일 때문에 10분 정도 늦었더니 시누이가 선을 넘고야 마는데    라디오사연  썰사연 사이다사연 감동사연</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>오늘의 반전</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>1.77천</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>1시간 29분</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>(반전 사연) 남편과 10년간 개고생하고, 성공해서 100평대 펜트하우스 계약하러 갔는데 내가 바로 이혼장에 도장찍고 웃어대자 그 이유를 알고 그자리에서 혼절하는데 사이다사연</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>따뜻한 차가움</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>1.71천</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1시간 58분</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2,236</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>친정에서 신혼집을 마련해준다니 시댁 근처에 집을 구해 시부 간병까지 하라는 시모..제대로 한방 먹이고 결국 파혼했습니다</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>smokey3030150</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>1.31천</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>1시간 10분</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2,480</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>(썰극장)친정에서 해준 신혼집을 공동명의로 해달라는 시모 다른뜻은 없고 우리 아들 명의로 집이 있으면 좋겠구나 그런데 왜 시댁집을 시숙님한테 준거에요?속내를 알게되고 한방 먹이는데</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>mrreignearth</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>1.28천</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>2시간 11분</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>Дорогая, завтра я привезу свою мать и сестру. Будут на тебя смотреть. Если дадут добро, то поженимся</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>사연인생극장</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>1.25천</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1시간 10분</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>친정아빠 발인날 남편은 가족들 앞에서 이혼서류 던지길래 저는 웃으며 제 건물을 팔았습니다 3일뒤, 시모의 다급한 전화 60통 “길바닥에서 노숙이라도 하라는거냐!”</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>세월의 이야기</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>1.21천</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>1시간 11분</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>남편이 1년 해외 출장 발령받아 비행기에 올랐는데,시어머니가 내 물건들을 밖으로 던지며,리모델링해 시동생 신혼집으로 쓰겠다고？남편이 떠나기 전 당부한 말이 생각나 참았는</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>심야의 고백</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>1.2천</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>1시간 28분</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>남편 빵집이 방송나와서 대박나자 이혼 강요하며 가방 내던진 시모 “식모는 니년말고도 널렸어! 당장 나가!” 저는 짐가방 챙겨서 떠났습니다 3일후, 기막힌 광경이 펼쳐지는데</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>고요한 밤</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>1.17천</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>1시간 40분</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>1,063</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>(반전 사연) 아빠 유산이 엄마에게 상속되자 자기 돈이라는듯 밤에 잠도 제대로 못 잔 남편 그때 오빠가 한마디 하자, 남편 인생 종 쳤습니다 /사이다사연/라디오드라마</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>오늘의 감동 이야기</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>1.15천</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>2시간 16분</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>682</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>친정엄마 장례식날 남편은 출장간다며 상간녀와 모텔 갔길래 저는 시모 병원비를 중단했습니다 다음날, 남편에게 걸려온 전화 99통 저는 말했죠 “누구세요？ 저 이혼했는데요？”</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Mecho Sladak</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>1.11천</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>1시간 17분</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>이혼도장 찍기전 내 뺨 때리고 머리채 잡고 뜯는 시어머니 “지긋지긋한 기생충년! 이젠 끝이다!” 저는 시댁 생활비를 끊었습니다 다음날, 하루종일 걸려오는 시모 전화</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>마음이야기방</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>1.11천</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>1시간 31분</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>(반전 사연) 혼자 25년동안 살던 재력가 엄마가 재혼한다고 하자 전전긍긍하던 남편 너무 이상해서 내가 뒷조사를 하자그 결과, 남편이 나락으로 떨어지는데 /사이다사연/라디오드라마</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>작약꽃</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>1.07천</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>1시간 49분</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>[반전 신청사연]출산날 내 회사가 부도난 사실에 이혼서류 들고 찾아온 시댁 식구, 이혼후, 뉴스에 내가 나오던 순간 이전 시댁이 뒷목잡고 쓰러지는데..</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>인생 드라마 사연</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>1.07천</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>2시간 24분</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>칠순 잔치 왔다고 며느리 뺨 때린 시어머니, 전화 한 통에 시댁이 완전히 몰락하는데… ｜ 오디오북 시니어사연 고부사연</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>오늘의 사연집</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>1.01천</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1시간 23분</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>시한부 친정엄마 며칠 모신다고 했더니 머리채 잡고 내 뺨때린 시모 “니 애미가 우리집 식구냐 당장 나가!” 저는 조용히 재산을 정리했습니다 며칠뒤, 풍비박산난 시댁</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>세월이야기</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>996</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1시간 22분</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>임신한 내연녀가 내 뺨 때리는데 “언니 이제 똥차 좀 빼줄래요!” 남편과 시모는 웃으며 구경만하길래 저는 시댁 집을 팔고 떠났습니다 며칠 뒤, 시댁은 풍비박산 나는데</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>시댁사연</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>972</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>1시간 54분</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>(반전 신청사연) 시부 칠순에 엄마가 5만원 드리자 뷔페 접시에 전복을 덜어내던 시모 시부가 한마디 하자 거품무는데/라디오드라마/사연/실화/사연의 품격/썰</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>MegaSushi77</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1시간 15분</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2,884</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>친정엄마 장례로 시모 환갑 못 가자 남편이 폭언했다 ＂죽은 사람이 더 중요해？! 당장 이혼해!＂＂그래, 이혼하자!＂하고 전화 끊자,몇 시간 뒤 남편은 오열하며 전화했다!</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Letterbombful</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1시간 8분</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>3,509</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>결혼 보름 만에 시어머니가 ＂이 집 우리 거니 월 300만 원 내라＂ 했다  침묵하는 남편을 보며 난 웃으며 말했다  ＂그럼 내 집으로 갈게요 ＂ 그리고 다음 날   ｜ 고부사연</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>숨겨진 사연극장</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1시간 21분</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>3,108</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>남편이 시부 재산 20억 상속받자 현금 2억 던지며 이혼하라는 시모 “너같은 거지년 필요없어! 당장 나가!” 저는 곧장 친정으로 갔습니다 다음날, 시모는 대성통곡 하는데</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>감정을 해소할 수 있는 곳</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>719</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>2시간 57분</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>'귀찮은 노인네' 라며 요양원에 보내고 최고급 호텔에서 장모 칠순잔치하는 아들과 며느리, 전 재산 상속 취소하고 알거지를 만들었습니다</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>이야기 머무다</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>668</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1시간 26분</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>1,388</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>모임 자리에서 변호사 며느리의 뺨을 때린 시어머니, 검사인 아들을 파면시키고 무릎을 꿇게 했습니다</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>카를로스 스토리아</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>3시간 13분</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>362</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>호텔 청소부 엄마 쫓아낸 아들과 며느리, “ 내가 호텔 회장인거 몰랐지？”</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>세상의 관점</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>1시간 17분</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>동생 수술비는 안 된다던 남편… 2주 뒤 시모 생일에 제가 한마디 하자 모두 얼어붙었다 | 실화사연</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>허태옥</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>537</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>2시간 37분</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>이혼 도장 찍자마자 저는 시댁에 들어간 제 투자금을 전부 회수했습니다 대박 난 식당의 진짜 주인이 며느리인 줄 모르고 식모 취급하던 시어머니와 전 남편은  바지가랑이를 붙잡는데</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>사연우체통</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>508</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>1시간 24분</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>암환자 며느리에게 시누이 돌잔치 맡긴 시어머니…남편이 드디어 폭발했다</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>사연파장</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>501</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>1시간 21분</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>친정아빠 칠순 생신에 다녀온 사이, 신혼집 비밀번호를 바꿔버린 시모 "다시 얼씬도 하지마라!" 저는 조용히 집을 팔아버렸습니다.. 며칠 뒤 역대급 반전이..</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>비밀재판소</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>1시간 19분</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>나보고 시누 아들 돌잔치 날 음식하라며 소리치는 미친시모 “며느리 두고 뭐하러 사람쓰니!” 잔치 전날 제주도로 여행 떠났습니다  빈 잔칫상에서 돌잡이하는 시댁식구들</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>복수의 밤</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>1시간 38분</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>60대 남성이 윗집에 사는 여성과 사랑에 빠지다: 황혼기의 로맨스, 재혼, 그리고 사랑 | 오디오북 &amp; 오디오 드라마</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>인생의 반전극</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>1시간 24분</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>234</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>친정 한우집에 친구들 50명 데려와 천 만원 어치 먹고 배째라는 시모 “새아가 사돈께 잘먹었다 전해라!” “네~ 근데 고깃집 이미 팔았는데요” 30초 뒤 시모는 대성통곡</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>시월드 사이다 극장</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>1시간 3분</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>딸네 집에 안경을 두고 와 다시 갔더니 시어머니가 딸 뺨을 때리고 있었습니다… 저는 비서실장에게 전화했죠 “김 실장, 준비한 대로 시작해주세요” | 고부갈등 사연</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>감성 사연라디오</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>1시간 2분</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>vip 모임에서 변호사 며느리의 뺨을 때린 시어머니, 검사 아들 파면시키고 무릎꿇게 했습니다</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>인생의 한 페이지</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>1시간 37분</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>친정엄마 신장이식 해주려 입원한날 내카드 훔쳐서 해외로 휴가간 시댁식구들무슨 상관이야 갔다가 장례치르던가저는 년놈들에게 복수를 다짐했습니다 며칠뒤시댁에서 걸려온 다급한전화</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">마음 사연방 </t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>2시간 12분</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>엄마 우리 살기도 빠듯해요  자식한테 짐 되지 말라며, 막말 내뱉는 아들며느리, 재산 싹 정리해버린 할머니ㅣ사연ㅣ오디오북ㅣ노후생활ㅣ인생이야기</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>사연우체통</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>1시간 4분</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>1,722</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>제가 1도 모르는줄 알고 상간녀 아이 돌잔치를 특급호텔 VIP룸에서 열어준 시모 '며늘아! 이번달 용돈 왜 안보냈니？' 저는 말했죠 '남한테 돈을 왜 줘요？'</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>오늘 이야기</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>1시간 18분</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>친정엄마 병원때문에 하루 자고간다니 현관 비밀번호 바꿔버린 남편 “병균 옮으니까 모텔에 재워!” 저는 말없이 집을 팔았습니다 며칠뒤, 빌빌기며 싹싹 비는 시댁식구들</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>달빛 라디오_Rad</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>2시간 22분</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>친정엄마 위독한데 친구들과 술 마시러 간다던 남편 "노인네 꾀병이네! 꼴값 좀 떨지마!" 보름 뒤 시모 환갑잔치엔 "누구세요 저 해외여행 중인데요" | 부부갈등 이혼 사연</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>인생이야기방</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>1시간 11분</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>시누이에게 3억 줬더니 개업식 오지 말라는 시댁, 저는 보증금을 빼고 가게를 내놨습니다</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>가족의 비밀극장</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>1시간 10분</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>(썰극장)결혼 3년만에 친정에 다녀왔는데 도어락 비번이 바껴서 남편한테 물으니 엄마가 바꾼거 같은데 친정에 가지 말랬잖아ㅎ 다음날 며느리 기강 잡겠다며 찾아온 시모가 싹싹비는데ㅋ</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>따뜻한 사연</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>1시간 35분</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>친정엄마 식당 건물을 통째로 사드렸더니 엄마 식당에서 동창회 한다고 100명 예약하고 안오길래 시모에게 전화하니 “비린내나서 고기집으로 바꿨다!” 시모에게 미친 복수를 시작했습니</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>붉은 장미의 복수</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>1시간 14분</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>[실화사연]자기 엄마 늙은것 같다고 이젠 아들 노릇 하고 싶다는 남편“엄마 살아봤자이십년이야!모시면서 좀 보살펴 드리고싶어!”짝짝짝~박수치며 만세 불렀습니다</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>삶의 따뜻한 조언</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>2시간 13분</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>30년 만에 동창회에 갔더니  딸년 법원 다니냐 비웃는 동창년 “커피 심부름이나 하겠네 ” 30분 뒤, 우리 딸 보더니 벌벌기며 살려달라 애원하는데</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>오늘의 가족드라마</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>1시간 18분</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>(썰극장)아빠 회사에서 일하던 남편이 이혼하자 아빠 거래처를 다 뺐고 회사를 새로 차리는데 나랑 이혼하면 니 아빠 회사 망할거라 했지ㅎ얼마 후 남편놈 인생 종쳤습니다ㅋ</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>사연극장</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>1시간 13분</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>시댁 김장날 김치로 며느리 뺨을 때린 시어머니, 다음날 남편의 회사가 뒤집혔습니다ㅣ고부갈등ㅣ부모자식ㅣ감동사연ㅣ오디오북ㅣ시니어사연ㅣ아들며느리ㅣ어머니ㅣ사연라디오ㅣ</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>행복한 노후 이야기</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>1시간 16분</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>30년 만에 동창회에 갔더니  딸년 법원 다니냐 비웃는 동창년 “커피 심부름이나 하겠네？” 30분 뒤, 우리 딸 보더니 벌벌기며 살려달라 애원하는데</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>인생역전 사연</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>1시간 26분</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>5년간 남편 뒷바라지 했는데 사업 대박나니 젊은애랑 바람난 남편 ＂무식한 너랑은 더 이상 못살겠다＂ 저는 웃으며 이혼도장 찍어줬습니다 2주 뒤, 찾아와 무릎 꿇은 남편</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>사연꽃길</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2시간 5분</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>며느리 빵집 빵 몽땅 버린 시모 보자기 하나 툭 놓고 가는데    ⧸ 고부갈등 ⧸ 오디오북 ⧸</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>참지 않는 며느리</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1시간 18분</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>식모처럼 부리던 며느리에게, 국정원 요원과 등장한 그룹총수가 90도 인사를하다니 | #노후사연 | #사이다사연 | #시니어사연 | #오디오북</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>인생의 결</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2시간 5분</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>며느리 빵집 빵 몽땅 버린 시모 보자기 하나 툭 놓고 가는데    ⧸ 고부갈등 ⧸ 오디오북 ⧸</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>참지 않는 며느리</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1시간 18분</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>식모처럼 부리던 며느리에게, 국정원 요원과 등장한 그룹총수가 90도 인사를하다니 | #노후사연 | #사이다사연 | #시니어사연 | #오디오북</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>인생의 결</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>1시간 7분</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>이혼한 시누이와의 합가를 거절했다가,시어머니에게 뺨을 세게 맞았고,남편마저 ＂다 당신 탓이야!＂라며 나를 원망했다 이에 나는 침착하게 전화 한 통을 걸었다 불과 1시간</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I82"/>
+  <autoFilter ref="A1:I84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -4795,12 +4707,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4821,54 +4737,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>채널이름</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>구독자</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>영상 수</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>시댁 소재 비율</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>1시간 이상 영상 비율</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>평균 길이</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>최근 30일 업로드</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>최근 10개 평균 조회수</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>조회수 1위 영상</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>썰이빛나는밤에</t>
         </is>
@@ -4908,14 +4824,14 @@
           <t>51,800</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>실화사연-강남살던 엄마가 돌아가시자 부동산으로 날 부른 남편 "장모님 집 엄마 주기로 했으니까 잔말말고 도장이나 찍어" 웃으며 도장을 찍자 서류를 본 남편이 파랗게 질려 싹싹비는데</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>커피엔톡</t>
         </is>
@@ -4955,14 +4871,14 @@
           <t>14,075</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>[실화사연] 전신마비가 된 남편과의 그날 방에서 믿을 수 없는 충격적인 것을 보게되는데…. 이성의 끈을 놓아버렸습니다|사연읽어주는|라디오드라마|썰라디오|라디오사연</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>사연튜브 • 사연라디오</t>
         </is>
@@ -5002,14 +4918,14 @@
           <t>56,100</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>(반전신청사연)재혼한 남편 죽고 남편자식을 눈물로키워 의사로 만들었는데"계모주제에 사돈대접 받고싶어요?" 예비사돈이 경악할말을 하자 아들이 사돈을[신청사연][사이다썰][사연라디오]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>랄라하의 사연드라마</t>
         </is>
@@ -5049,14 +4965,14 @@
           <t>25,900</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>미혼모로 낳은 딸이 검사가 되어 상견례를 하게 되는데, 예비 사부인이 나를 깔보며 애 아빠를 공개하라며 "근본을 알아야 사람이죠! 안그래요?" 그 순간 방문이 열리자 역대급 반전이</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>썰티비</t>
         </is>
@@ -5096,14 +5012,14 @@
           <t>47,020</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>(반전사연)남편 혼자 1년 해외출장을 간다며 나한테 말도없이 집을 팔고 시모를 모시라는데..내가 보낸 사진에 게거품 물면서 귀국하는데ㅋ[신청사연][사이다썰][사연라디오]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>사연읽어주는남녀</t>
         </is>
@@ -5143,14 +5059,14 @@
           <t>28,130</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>일본온천여행 가자던 아들내외가 나를 이국땅에 버리고 사라지는데 아들 보다 더 빨리 집에 찾아와 도어락 새로 달아 비밀번호 바꾸고 아들 며느리 짐 싸서 내다 버렸습니다</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>사연을 부탁해</t>
         </is>
@@ -5190,14 +5106,14 @@
           <t>15,030</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>[결혼파혼썰] 결혼할 남친집 인사 갔다가 충격받고 파혼 합니다 l 썰ㅣ파혼ㅣ사이다썰ㅣ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>사연속으로</t>
         </is>
@@ -5237,14 +5153,14 @@
           <t>41,230</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>추석날 나만 주방에 두고 외식 하러 가며 시모가 하는 말 "우린 밥 먹고 올테니 전 다 부쳐놔라" "네 천천히 드시고 오세요" 외식 후 돌아온 남편과 시모 오열하며 바닥을 기는데</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>사연 방송국</t>
         </is>
@@ -5284,14 +5200,14 @@
           <t>23,600</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>(실화사연) 오랜만에 만난 고향친구가 내 아내를 섬에서 봤다길래 "내 아내는 7년 전에 죽었는데..?" 그 즉시 배를 타고, 그 섬에 내린 순간 기함할 광경에, 입을 틀어막았습니다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>인생튜브</t>
         </is>
@@ -5331,14 +5247,14 @@
           <t>37,040</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>형수님이 싸준 음식만 버리는 임신한 아내가 의심스러워 몰래카메라를 설치했더니ㅣ노후사연ㅣ고부갈등ㅣ사연라디오</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>돌고 도는 시월드</t>
         </is>
@@ -5378,14 +5294,14 @@
           <t>12,023</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>정말 "밥"만 해놓은 시어머니.. 참교육</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>톡톡사이다</t>
         </is>
@@ -5425,14 +5341,14 @@
           <t>13,610</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>[톡톡사이다] 시댁 행사에 온갖 핑계로 오지 않는 막내 동서를 참 교육해보자~ 요새 애들 왜이러니?</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>작은별 라디오</t>
         </is>
@@ -5472,14 +5388,14 @@
           <t>24,000</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>[반전사연]  시댁 과서원 가격이 30배가 오르자 나보고 이혼해달라는 정신나간 상간녀, 바로 도장찍고 역대급 복수 해줬습니다  [신청사연][사연라디오][사이다썰]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>함께걷는시간</t>
         </is>
@@ -5519,14 +5435,14 @@
           <t>1,070</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>며느리만 보면 괴롭히더니 후회하는 시어머니#78탄~52탄외 무개념시어머니 몰아보기#고부갈등#시어머니며느리#가족#부부#씨월드#드라마#쇼츠</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>썰닭</t>
         </is>
@@ -5566,14 +5482,14 @@
           <t>6,280</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>보이스피싱 실제 통화</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>사연열차</t>
         </is>
@@ -5613,14 +5529,14 @@
           <t>4,120</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>(실화사연)두 형부가 정비사 남편을 개무시하며 "자네 시간나면 내 외제차에 기름 좀 넣어놔ㅋㅋ" 남편이 황급히 미국땅 밟고 한국에 돌아오는 순간, 두 형부가 무릎을 꿇고 비는데..</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>매운맛 인생사</t>
         </is>
@@ -5660,14 +5576,14 @@
           <t>9,150</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>아빠 장례 치른 후 엄마와 나 고생했다며 해외 보내 준 남편, 공항에 가는 길 엄마가 "차 돌려라! 박서방 수상하다" 엄마 말대로 시댁 쳐들어가자 막장 광경이 펼쳐졌습니다</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>깡냉이톡썰</t>
         </is>
@@ -5707,14 +5623,14 @@
           <t>17,870</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>깡냉이톡썰 몰아보기 - 사이다사연 &amp; 참교육 모음 1편</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>배신의 장미</t>
         </is>
@@ -5754,14 +5670,14 @@
           <t>3,150</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>[실화 사연] 우리 시어머니 고아라고 무시하고 시집살이 시키더니, 제사에 차례까지 지내라고? 시조모님 시숙부님 미치셨어요? 내 시모는 내가 지킨다. 모두 꺼져주세요.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>썰담집</t>
         </is>
@@ -5801,14 +5717,14 @@
           <t>1,362</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>사이다사연-엄마 장례식에 불참한 시댁식구들이 유산으로 남긴 45평 집을 보고 염치 없게 같이 살자고 요구를 하는데.. 거절하니 내 멱살을 잡네요? 잡것들 다 차단하고 손절했습니다ㅋ</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>썰크림 영상툰</t>
         </is>
@@ -5848,14 +5764,14 @@
           <t>286,000</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>명절에 며느리 부려먹으려고 친정안보내는 시어머니 사연  |  사이다 복수사연 &amp; 재밌는 사연 모음</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>해바라기사연방, 썰라디오 사연읽어주는여자</t>
         </is>
@@ -5895,14 +5811,14 @@
           <t>13,832</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>[실화 사이다 복수사연] 며느리를 욕하는 시어머니의 귀싸대기를 친정엄마가 갈겼습니다. 며느리를 몸종처럼 생각하는 경우없는 시어머니와 남편의 버릇을 고쳐놨어요./실화사이다사연/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>돌고 도는 톡툰</t>
         </is>
@@ -5942,14 +5858,14 @@
           <t>5,720</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>★ [풀영상] 명절만 되면 개처럼 며느리 부려먹는 시댁</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>유머명가</t>
         </is>
@@ -5989,14 +5905,14 @@
           <t>9,450</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>며느리 카드로 8명 항공권 결제한 시댁, 반복된 카드 도용과 마일리지 가로채기 계획까지 들통난 사이다 참교육</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>사연많은유튜브</t>
         </is>
@@ -6036,14 +5952,14 @@
           <t>10,809</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>[사이다사연]아들내외 서울에 집사주고 병원때문에 두달에 한번 들리니"아들집 자주 오는거 몰상식하니 호텔가라"네요?괘씸해서 부동산 전화했네요"집 내놓으려고 하는데요"[사만유]</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>한수연의 사연 채널</t>
         </is>
@@ -6083,14 +5999,14 @@
           <t>317</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>(사이다사연) 친정에서 사준 47평 아파트에 시누네 가족을 들이라는 시모에게 참다못한 며느리가 참교육하는데 | 라디오드라마 실화사연</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>둥이둥이썰TV</t>
         </is>
@@ -6130,14 +6046,14 @@
           <t>3,430</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>부모님이 해주신 집에서 같이 살고 싶다는 예비 시부모님. 거절했더니 시누이까지 연락을 해왔습니다. (+추가/후기)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>저혈압치료툰</t>
         </is>
@@ -6177,14 +6093,14 @@
           <t>108,400</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>사이다툰 모음집│시어머니 며느리의 역지사지 참교육 복수전│영상툰</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>그대는청춘</t>
         </is>
@@ -6224,14 +6140,14 @@
           <t>51,868</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>시장통 건달 참교육하는 시어머니와 며느리 본편(2부)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>일상속신박한사연들</t>
         </is>
@@ -6271,14 +6187,14 @@
           <t>876</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>[핵사이다사연] 명절에 시댁에서 칼춤 추고 친정 갔어요.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>한입썰</t>
         </is>
@@ -6318,14 +6234,14 @@
           <t>9,090</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>며느리의 시월드 탈출기, 독립선언 &amp; 복수혈전 시리즈(1편~6편) 몰아보기 #시월드 #고부갈등 #참교육 #반전 #이슈 #드라마 #공감 #독립선언 #복수혈전</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>며느리시어</t>
         </is>
@@ -6365,14 +6281,14 @@
           <t>9,550</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>예비며느리 결혼 반대 했다가 100억 날릴뻔한 예비시어머니</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>별별사연툰</t>
         </is>
@@ -6412,14 +6328,14 @@
           <t>52,200</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>🔥톡툰🔥 아파트 뺏고 연금 뺏어가는 아들 며느리..속시원한 결말 사이다툰 시댁썰 결혼썰</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신바람 사연아파트</t>
         </is>
@@ -6459,14 +6375,14 @@
           <t>26,500</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>[사이다사연] 후회할 이혼보단 깔끔한 파혼이 낫지요 (실화사연/사이다 실화사연)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>도라마열차</t>
         </is>
@@ -6506,14 +6422,14 @@
           <t>3,084</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>갑질 개막장 지옥같은 시월드에서 내 아내 구하는 멋진 남편 모음 #시어머니 #며느리 #시월드 #시댁갈등 #멋진남편</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>인생을 말하다</t>
         </is>
@@ -6553,14 +6469,14 @@
           <t>105</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>며느리 앞에선 엄마도 사람 취급 못 받아요"… 설날 찾아갔다가 문전박대당한 어머니의 반격</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>집안사연</t>
         </is>
@@ -6600,14 +6516,14 @@
           <t>621</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>남편이 세상을떠나면서 남기고간 18억을 아들 딸들이 어떻게든 가져갈려고하자 어머니가 행동한 복수 | 오디오북 | 노후사연 | 인생이야기 | 재산상속 | 재산증여</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>시어머니와 며느리</t>
         </is>
@@ -6647,14 +6563,14 @@
           <t>168</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>69세인 저는  5,500만 원의 예금을 들고 아들 집에 노후를 보내러 갔습니다. 손주에게 밥을 먹여주던 순간, 무심코 그만…</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>톡툰 스토리</t>
         </is>
@@ -6694,14 +6610,14 @@
           <t>6,592</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>눈 오는 밤 굶주린 조카를 거뒀더니 20년 뒤 강남 아파트를 사줬는데.. 집들이에 나타난 동서의 첫마디가 충격</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>사연라디오 세모사모 : 세상의모든사연모음</t>
         </is>
@@ -6741,14 +6657,14 @@
           <t>37,180</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>소름돋는 남편의 이중생활과 본색을 드러내는 시어머니.. | 시댁이야기 | 사연라디오 | 남편바람 | 남편외도 | 사이다사연 | 레전드사연 | 네이트판</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>사연 한그루</t>
         </is>
@@ -6788,14 +6704,14 @@
           <t>15,870</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>33평 아파트로 이사한 친구, 집들이에서 나타난 솔직한 본성</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>배신의 후리지아</t>
         </is>
@@ -6835,14 +6751,14 @@
           <t>1,430</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>[카카오실화사연]결혼하는 시누이 집과 결혼비용안해준다 했더니 징징대며 시가로가 버린 남편.남편말 들어주고 얼른집으로 데리고 가라는 시모.그냥끼고 살아요.그런 징징이는 필요 없어요</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>비둘기툰</t>
         </is>
@@ -6882,14 +6798,14 @@
           <t>68,000</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>며느리 돈으로 놀고 먹는 시댁과 시누이 │모음집│고부갈등│사이다썰│통쾌한복수</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>촛불</t>
         </is>
@@ -6929,14 +6845,14 @@
           <t>530</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>중졸인 며느리를 직원으로 받아준 부도직전 시아버지, 며느리의 정체에 모두 놀라는데</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>한국 재벌의 세계</t>
         </is>
@@ -6976,14 +6892,14 @@
           <t>7,145</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>VIP실 전 시어머니가 "정오까지 병원비 입금해." "잘못 거셨어요." 30분 뒤 전남편에게 온 전화. "보증인이 지난주에 이름 뺐습니다." 그는 하얗게 질렸다.ㅣ노후사연ㅣ감동사연</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>인생비밀창고</t>
         </is>
@@ -7023,14 +6939,14 @@
           <t>16,170</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>이혼 하자마자 병원장 딸과 재혼한 전남편 5분뒤 병원 문 닫게 했습니다</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>인생사연</t>
         </is>
@@ -7070,14 +6986,14 @@
           <t>344</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>쫓아낸 며느리 회사인줄 모르고 찾아온 시어머니 '당장 이사장 불러!' '부르셨어요？'</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>공주 이야기005</t>
         </is>
@@ -7117,14 +7033,14 @@
           <t>204</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>(반전사연)남편의 갑작스러운 이혼 선언에 남편회사 비서한테 물어봤더니 여자가 있다는데..상간녀를 확인한 순간 쾌재를 부르며 도장을 찍어주는데ㅋ[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>잼썰</t>
         </is>
@@ -7164,14 +7080,14 @@
           <t>2,950</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>(실화사연) 친정아버지 회사에서 갑질을 하던 시누이의 머리채를 낚아 챈 시모 [라디오드라마][사이다사연]</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>눈물의 사연</t>
         </is>
@@ -7211,14 +7127,14 @@
           <t>995</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>(반전 사연) 내가 번 돈으로 신축아파트를 들어가자 나보다 먼저 이삿짐 옮긴 시댁식구 백수 남편도 어깨펴며 모신다고 하길래 온 시댁을 불바다로 만들어 버리는데 사이다사연</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>마루아라 상담소</t>
         </is>
@@ -7258,14 +7174,14 @@
           <t>5,104</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>친정 부모를 '거기'라 부르던 시어머니, 돌잔치 마이크 잡은 며느리 앞에 연회장이 얼어붙는데..ㅣ고부갈등ㅣ인과응보ㅣ며느리사연ㅣ사연라디오ㅣ오디오북</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>인생그날</t>
         </is>
@@ -7305,14 +7221,14 @@
           <t>9,277</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>독박 병수발 10년차 며느리만 빼고 칠순 여행 하와이 간 시댁, 이혼하려 짐 싸는데 시아버지가 건넨 봉투에는....ㅣ노후사연ㅣ인생사연ㅣ오디오북ㅣ감동사연ㅣ고부갈등</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>토리토리이야기</t>
         </is>
@@ -7352,14 +7268,14 @@
           <t>13,830</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>아버지 팔순잔치 비용을 혼자 다 낸 셋째 // 사이다툰ㅣ영상툰ㅣ시댁썰ㅣ사연ㅣ썰ㅣ썰툰ㅣ사이다썰ㅣ시댁ㅣ시원</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>스토리YOON</t>
         </is>
@@ -7399,14 +7315,14 @@
           <t>3,710</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>신혼인데 남편이 음료수 하나로 화내더니… 시누이 문자 보고 결혼을 다시 생각했습니다 실화 사연</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>타임원탑</t>
         </is>
@@ -7446,14 +7362,14 @@
           <t>183</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>예비며느리 시험하러 은행에 갔다가 지점장에게 뺨맞는 며느리를 본 은행장 시아버지ㅣ인생라디오ㅣ노후사연ㅣ오디오북ㅣ시니어사연</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>화제의톡톡 166</t>
         </is>
@@ -7493,14 +7409,14 @@
           <t>187</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>와이프가 갑자기 임신했다네요  사실 나는 무정자증인데   바람피운 와이프 참교육 들어갑니다  실화사연 라디오사연 참교육 반전</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 사연중독</t>
         </is>
@@ -7540,14 +7456,14 @@
           <t>11,970</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>명절에 시댁식구 30명, 시모는 상차림이 왜 이모양이냐?  어머님이 하시던가요,, 저는 상을 엎어버렸습니다..</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>화제의톡톡 167</t>
         </is>
@@ -7587,14 +7503,14 @@
           <t>84</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>속도 위반으로 결혼한 시누이의 혼수가 우리집으로 들어오는데   무개념 시누 참교육</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>꽃길이야기</t>
         </is>
@@ -7634,14 +7550,14 @@
           <t>40</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>화분 밑에서 나온 소름 돋는 비밀, 66세에 재혼을 했지만 그냥 혼자 살걸 눈이 멀었었나 봅니다</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>감정몰입극장</t>
         </is>
@@ -7681,14 +7597,14 @@
           <t>153</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>"장남 기 살려야지" 전 재산 20억 아들 주고, 딸에겐 "니가 병수발해라"</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>그때 그사연</t>
         </is>
@@ -7728,14 +7644,14 @@
           <t>601</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>결혼식 끝나자마자 쫓아낸 시댁, 28분 뒤 전원 길거리로 나왔습니다</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>톡톡밀크티</t>
         </is>
@@ -7775,14 +7691,14 @@
           <t>281</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>고아라고 무시당하며 산 며느리 앞에 30년만에 나타난 친아빠의 실체에 인생의 반전이 찾아오는데...</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>반전 대화</t>
         </is>
@@ -7822,14 +7738,14 @@
           <t>94</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>(반전사연)친정에서 집을 해주기로해서 남편한테 혼수를 얘기하니 혼수는 당연히 여자가 하는거라는데..한방 먹이고 빠른 파혼 합니다[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>시절인연이야기</t>
         </is>
@@ -7869,14 +7785,14 @@
           <t>104</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>"감히 어디서 고졸이!" 구박받던 며느리, 이혼 후 강남 빌딩 7채 재벌로 나타나 시댁 참교육</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>인생오디오</t>
         </is>
@@ -7916,14 +7832,14 @@
           <t>152</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>이혼합의 18년 후 서울대 입학식 전처 아들의 한마디에 재벌회장은 숨이 멎는데</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>동치미 극장</t>
         </is>
@@ -7963,14 +7879,14 @@
           <t>1,558</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>"네까짓 게 감히?" 며느리·약자 무시하다 인생 탈탈 털린 진상들의 충격적 최후 모음집🔥[1시간 연속보기]</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>인생뒤집기</t>
         </is>
@@ -8010,14 +7926,14 @@
           <t>18</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>반전사연시누가 아이를 낳았다며 친정에서 해준 30평 아파트를 시누 15평 아파트랑 바꾸라는 시모  시댁 편드는 남편까지 초토화 시켰습니다라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>사연의 마지막 장면</t>
         </is>
@@ -8057,14 +7973,14 @@
           <t>774</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>반전사연엄마사업이 힘들다고 하자 파혼하자는 예비남편  엄마를 처음본 예비시부가 엄마한테 인사하자 예비남편놈이 게거품을 무는데ㅋ라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>일상 이야기</t>
         </is>
@@ -8104,14 +8020,14 @@
           <t>65</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>【실화사연】 바람펴서 10년전에 이혼한 예전 아내에게서 다시 합치자는 연락이 왔다... 아직도 상황파악 안되는 그녀의 최후 ㅋㅋ</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>깨소금상회</t>
         </is>
@@ -8151,14 +8067,14 @@
           <t>82,418</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>돈봉투를 쳐 낸 명품 매장 직원… 할아버지는 상견례부터 하자고 했습니다</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>숨겨진 톡</t>
         </is>
@@ -8198,14 +8114,14 @@
           <t>486</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>(반전사연)결혼 전 친정에서 해준 아파트랑 시모가 살고 있는 빌라랑 바꾸자는 예비남편..대리 효도 하려는 남친놈 한방 먹이는데..[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>시월드 한방</t>
         </is>
@@ -8245,14 +8161,14 @@
           <t>2,310</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>신혼여행에서 돌아오자 시모가 “아침밥 차려!”—남편까지 내쫓고 내가 이혼한 진짜 이유</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>진실노트</t>
         </is>
@@ -8292,14 +8208,14 @@
           <t>624</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>반전사연예비 남편이랑 결혼전인데 시누가 먼저 결혼한다며 차를 사달라고 하는데  남편놈은 점수를 따라며 사주라고  파혼한다 하니 싹싹비는데ㅋ라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>마지막 대화</t>
         </is>
@@ -8339,14 +8255,14 @@
           <t>37</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>(반전사연)상견례에서 친정아빠가 건설현장에서 일한다고 결혼을 반대한 시모..아빠가 타는 고급승용차를 보고 태도가 돌변해서 결혼시키자는데..꺼져라[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>가족사연오디오북</t>
         </is>
@@ -8386,14 +8302,14 @@
           <t>684</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>시어머니 서랍에서 발견한 며느리의 어린시절 사진...며느리를 차갑게 대했던 진짜 이유! 20년만의 진실 |노후사연ㅣ감동사연ㅣ사연라디오ㅣ오디오북</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>그날의 진실</t>
         </is>
@@ -8433,14 +8349,14 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>시누이 집들이에 8시간 달려갔는데 음식 한 점 없었습니다… 남편의 한마디에 모든 것이 끝났습니다</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>사연의 끝</t>
         </is>
@@ -8480,14 +8396,14 @@
           <t>161</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>(사연열차)시모의 병수발 때문에 합가를 준비하던 중 친정부모님과 제주도를 가는데.."저기 사돈댁 아니니? 거짓말치고 합가하려던 남편과 시부모까지 참교육 시키고 이혼합니다!#실화사연</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>사연열전</t>
         </is>
@@ -8527,14 +8443,14 @@
           <t>1,714</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>이혼 9년 후 재혼, 호텔에서 마주친 전남편 “재혼하려고 애를쓴다 애를써”. 순간 새남편 등장에 전남편은 그 자리에서 개쪽 당합니다.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>톡톡 썰라디오</t>
         </is>
@@ -8574,14 +8490,14 @@
           <t>455</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>내 여친을 뺏은 전적이 있는 놈에게서 오랜만에 연락이 왔다 → 내 지금 여친이랑 아기가 생겼다고! 정말 너무 고마워! ㅜㅜ</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>사이다 인생사연</t>
         </is>
@@ -8621,14 +8537,14 @@
           <t>3,811</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>💥시아버지 환갑잔치에서 시어머니가 며느리의 뺨을 때리고, 남편은 쓰러진 아내에게 사과하라고 다그쳤다… 그녀는 말없이 식당을 나섰고, 며칠 뒤 모든 것을 조용히 준비해 두었는데… 😨</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>따뜻한 사연집</t>
         </is>
@@ -8668,14 +8584,14 @@
           <t>795</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>반전사연예비 남편 연봉을 모르고 있었는데 시모가 아들 연봉이 5천이라며 떠 받들고 살라는데  내 정체를 밝히자 미안했다며 싹싹비는데ㅋ라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>사이다 리벤지</t>
         </is>
@@ -8715,14 +8631,14 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>저와 상의도 없이 시댁 식구 6명을 집으로 들인 남편, 퇴근 후 밥 차려주기만을 기다리던 그들에게 딱 '이것' 하나 했더니 다음 날 집안이 풍비박산 났습니다</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>화제의톡톡 169</t>
         </is>
@@ -8762,14 +8678,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>명문대 나왔다며 고졸인 나를 무시하며 죄다 뺏어가려는 동서 참교육!!'형님, 좋은 말 할때 비번 원래대로 바꿔요  형님가방 내꺼, 내껀 원래 내꺼! 실화사연 라디오사연 참교육 반전</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>제이의사연</t>
         </is>
@@ -8809,14 +8725,14 @@
           <t>946</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>시댁 9식구 식사 준비하고 있는데, 남편이 갑자기 이혼을 요구했다. 나는 바로 앞치마를 벗어던지고, "어머님 아들이 절 버렸으니,이제 식사는 직접 알아서 하세요!"</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>오늘도 반전</t>
         </is>
@@ -8856,14 +8772,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>(반전사연)결혼전에 시댁이 이사 간다며 가전 제품을 내 카드로 결제한 예비남편..얼마 후 예비남편 카드로 아빠차를 결제했더니 게거품을 무는데ㅋ[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>인생담론</t>
         </is>
@@ -8903,14 +8819,14 @@
           <t>8,458</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>아빠가 보증을 잘못 서서 60억 친정집이 경매에 넘어갔다 하자, 청첩장 찢으며 파혼하잔 예비남편 "빈털터리랑 결혼할 뻔했네" 10분 뒤 배꼽 잡을 광경이 펼쳐지는데</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>모든 날</t>
         </is>
@@ -8950,14 +8866,14 @@
           <t>109</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>공장 집 딸이라고 5년을 식모처럼 부려먹던 시댁, 이혼 후, 바로 결혼식하는 전남편보고 전화 한통으로 시댁을 개박살냈습니다.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>눈물 끝에 핀 꽃</t>
         </is>
@@ -8997,14 +8913,14 @@
           <t>1,755</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>가족회의에서 며느리에게 무릎 꿇고 사과문 읽으라던 시어머니… 30년 가정부가 식탁 밑 녹음기를 꺼냈다ㅣ노후사연ㅣ감동사연ㅣ오디오북</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>노터치시월드</t>
         </is>
@@ -9044,14 +8960,14 @@
           <t>5,165</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>시어머니·시누이는 소파에… 며느리 혼자 전 부치라길래 명절 음식을 주문했습니다</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>어른의 지혜</t>
         </is>
@@ -9091,14 +9007,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>《정약용 명언》 부자가 되는 여성의 머리 스타일 5가지  이 습관만 지켜도 평생 재물이 모입니다</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>진실사연 - 여운</t>
         </is>
@@ -9138,14 +9054,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>(반전 사연) 혼인신고도 안한 예비며느리인 나한테 시댁식구들이랑 같이 살집 사오라던 시부 “내 병수발 하려면 같이 사는게 편하다 친정아빠가 나타나, 상상 초월한 복수를 선물하는데</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>사연은행</t>
         </is>
@@ -9185,14 +9101,14 @@
           <t>492</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>세쌍둥이 만삭 며느리한테 욕하고 떡국 500인분 시킨 시댁, 친정아버지가 시댁 개박살냈습니다</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>시월드의 민낯</t>
         </is>
@@ -9232,14 +9148,14 @@
           <t>13,476</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>엄마 장례 끝나자 친정집에 짐 풀던 시모… “시댁은 장남 줬어” 진짜 집주인 밝히자 얼어붙었다</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>@인생참맛-사연라디오</t>
         </is>
@@ -9279,14 +9195,14 @@
           <t>212</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>고부갈등 ㅣ추석날, 며느리 때문에 울어버린 시어머니 l 쫓겨난 며느리의 최후 #오디오북#노후사연#사연라디오#인생참맛#실화사연 #며느리시어머니 #명절 #시니어사연 #추석며느리</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>사이다인생극장</t>
         </is>
@@ -9326,14 +9242,14 @@
           <t>415</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>24년간 믿었던 아내의 충격적인 외도, 상대는 전혀 상상도 못한 인물이었습니다                                불륜사연 ｜ 오디오북 ｜ 복수사연 ｜ 사연낭독</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>썰튜브:사연라디오</t>
         </is>
@@ -9373,14 +9289,14 @@
           <t>54</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>"월급 280이라서 버렸습니다" 3년 만난 남친을 버린 여자, "이 것" 다시 붙잡고 싶습니다.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>드라마인생</t>
         </is>
@@ -9420,14 +9336,14 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>[황혼의 배신] 100억 유산 후… 떠난 아내, 무너진 남편앞에서 꺼낸 한마디.. [드라마인생 07편]│노후사연│황혼실화│황혼실화│황혼이혼│막장│사연│읽어주는 소설│라디오드라마│</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>shinnshienna</t>
         </is>
@@ -9467,14 +9383,14 @@
           <t>30</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
         <is>
           <t>부자집에 시집간 동생이 이혼 후 위자료 5억을 받자 남편은 시누 신혼집을 사주자고... 바람핀 남편에 이혼소송</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>끝까지</t>
         </is>
@@ -9514,14 +9430,14 @@
           <t>610</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>반전사연예비시댁 식구들이 모두 모였다 해서 인사갔더니 다들 한우를 먹는데 난 컵라면 끓여준 시모  친척이 날 보고 기겁하자 시모가 쓰러지는데라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>가족의비밀노트</t>
         </is>
@@ -9561,14 +9477,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>반전사연10년동안 거지처럼 살면서 마련한집을 자기 신혼집으로 한다며 좋아하는 시누  얼마 후 남편 몰골을 본 시누가 게거품을 무는데ㅋ라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>가족의비밀</t>
         </is>
@@ -9608,14 +9524,14 @@
           <t>16</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>반전사연남편 사장 취임 기념으로 파티를 하는중 상간녀와 함께 등장한 시모가 이혼하라는데 아빠한테 전화를 걸자 시모 얼굴이 새파랗게 질리는데ㅋ라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>따뜻한 사연집</t>
         </is>
@@ -9655,14 +9571,14 @@
           <t>482</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>반전사연시댁이랑 여행갈 때는 남편이 다 부담하는데 친정에는 돈 한푼 안쓰는 남편 아빠가 숨겨둔 재산을 공개하자 잘하겠다는 남편놈 한방먹이는데라디오드라마사연라디오카톡썰...</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>오늘의 사연 JC</t>
         </is>
@@ -9702,14 +9618,14 @@
           <t>93</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>반전사연5년동안 시모랑 살면 집을 사준다던 시모는 시누 신혼집이 급하다며 5년을 더 기다리라는데  평생 같이 살자는 남편놈 뺨을 날렸습니다라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>그날의 톡</t>
         </is>
@@ -9749,14 +9665,14 @@
           <t>725</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>반전사연결혼하고 처음 신혼집에 놀러온 친동생을 내쫓은 남편한테 뭐라했더니 내 동생이 예의가 없다는데  얼마 후 뻔뻔하게 시누를 데려온 남편놈라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>레몬소다 톡톡</t>
         </is>
@@ -9796,14 +9712,14 @@
           <t>295</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>(반전사연)엄마 생일에 찾아뵙지도 않고 3만원 이체한 남편..시모 생일에 내가 똑같이 하자 게거품을 무는데..내로남불 끝판왕 남편놈 한방먹이는데[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>인생사연소식</t>
         </is>
@@ -9843,14 +9759,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>정신병 취급하는 사돈 일가에 대항하는 시어머니의 복수. 노년의 삶의 지혜 행복한 노후생활 부모자식갈등 사연 이야기</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>그림자 속 진실</t>
         </is>
@@ -9890,14 +9806,14 @@
           <t>174</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>(반전사연)아빠 퇴직금으로 남편 사업 밀어줬더니 개업식날 이혼서류에 도장 찍으란 시모.10분 뒤 배꼽잡을 광경이 펼쳐지는데ㅋ[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>인생공부</t>
         </is>
@@ -9937,14 +9853,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>34년전 첫사랑의 장례식에 달려간 재벌회장 쌍둥이 상주의 얼굴을 보고 경악했습니다  오디오드라마 가족사연 감동사연 노후사연 반전사연 오디오북</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>뜻밖의 인생사연</t>
         </is>
@@ -9984,14 +9900,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I110" s="5" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>택시기사 딸이라고 결혼식에서 머리채 잡은 시어머니 다음날 시댁 건물 전부 사라져버리는데...                                   ｜ 반전사연 ｜ 오디오북</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>사연의 막간</t>
         </is>
@@ -10031,14 +9947,14 @@
           <t>502</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>10억 유산에 눈먼 시모가 “아들 몫 5억 내놔!” 결국 쫓겨난 남편이 시모 멱살을 잡았다</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>Alondra Daisy</t>
         </is>
@@ -10078,14 +9994,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>어린 장모님의 그곳을 건드리고 부부처럼 몇번씩을 실화사연 드라마사연 라디오사연 사연읽어주는 네이트판</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>인생 사이다썰</t>
         </is>
@@ -10125,14 +10041,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>반전사연명절에 예비시댁에 갔더니 앞치마를 던지며 설거지 하라던 예비시모  시누가 놀라며 내 명함을 시모한테 보여주자 입을 틀어막는데ㅋ라디오드라마사연라디오카톡썰</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>노후 사연 라디오</t>
         </is>
@@ -10168,14 +10084,14 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>"시댁은 왜 이렇게 힘들게 살아요?" 못된 며느리의 악행, 상속으로 갚아준 시어머니의 사이다 복수ㅣ노후사연ㅣ고부갈등ㅣ오디오북ㅣ가족갈등ㅣ중년고민 #고부갈등 #노후사연</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>우리 가족 이야기</t>
         </is>
@@ -10211,14 +10127,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>반전사연  큰오빠 세상떠난 충격에 쓰러진 엄마를 모셔온다하자 다음날 시모 먼저 모셔온 남편  신청사연사연라디오사이다썰</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>가족의 속마음</t>
         </is>
@@ -10254,14 +10170,14 @@
           <t>17</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>반전사연 언니 이민가고 동탄 집 비었단 소식에 다음날 새벽 시모에게 급한 연락이 오는데, 내가 입을 열자 시댁이 발칵 뒤집히는데 신청사연</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>사연극장</t>
         </is>
@@ -10297,14 +10213,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>실화사연돈 잘 버는 동서한테는 찍소리도 못하면서 내가 잘해주자 동서네 김장까지 나한테 다 시키는 시모  시댁이랑 연 끊겠다하니 시모가 비는데신청사연사이다썰사연라디오</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>사연 이야기 방송국</t>
         </is>
@@ -10340,14 +10256,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>실화사연 산부인과 의사인 동서에게 설거지 부탁하자 내뺨 후려친 시모 ＂급도 안되는년이 감히 누굴시켜!＂ 동서가 벌벌떨며 내 정체를 말하자 온시댁이 내게 납짝 엎드리는데ㅋ</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>진실의 끝</t>
         </is>
@@ -10383,14 +10299,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>(반전사연)내가 시모식당에서 일해야 시모 건물을 주겠다고 한다며 회사를 그만두라는 남편..남편이 회사를 그만둔 날, 시모가 남편 머리채를 잡는데[라디오드라마][사연라디오][카톡썰]</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>Jalisa Carlyle</t>
         </is>
@@ -10426,7 +10342,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I120" s="5" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>[사이다사연] 장례식장에서 상중인 우리 언니 소개시켜달라던 남편의 직장상사.. (실화사연_사이다 실화사연)</t>
         </is>
@@ -10678,7 +10594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10699,54 +10615,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>채널이름</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>구독자</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>영상 수</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>시댁 소재 비율</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>1시간 이상 영상 비율</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>평균 길이</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>최근 30일 업로드</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>최근 10개 평균 조회수</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>조회수 1위 영상</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>EBSCulture (EBS 교양)</t>
         </is>
@@ -10786,14 +10702,14 @@
           <t>3,262</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>“동화 아니야?” 산에서 작은 동물들 데려와 돌봐주는 천사 리트리버. 설쌤이 알려준 그 이유 #몰아볼교양</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>동치미</t>
         </is>
@@ -10833,14 +10749,14 @@
           <t>12,362</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>"공부를 너무 못해서 미국으로 보냈는데.." 겨우 대학교 입학 시켰더니 등산 갔다 추락해서 대학 중퇴했다는 아들 l #TALK 쏘다</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>잔잔한 사연집</t>
         </is>
@@ -10880,14 +10796,14 @@
           <t>23,000</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>명절마다 며느리를 하녀처럼 부리던 시댁, 화상 입은 손까지 부려먹자 남편이 결국 제사를 없애버렸습니다</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>쥐쥐극장</t>
         </is>
@@ -10927,14 +10843,14 @@
           <t>204,000</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>통쾌한 복수&amp; 재밌는 일상 사연 모음</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>당당이의 하루</t>
         </is>
@@ -10974,14 +10890,14 @@
           <t>2,862</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>절대 건드리면 안 될 아내를 쫓아낸 남편이 받은 참교육#부부#사랑#가족#참교육#사이다#드라마#시니어</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>봉이언니 썰툰</t>
         </is>
@@ -11021,14 +10937,14 @@
           <t>179,400</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>🍾먹는걸로 며느리 차별하는 시어머니 사이다 참교육!!!🍾 [영상툰I사이다툰]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>코기툰</t>
         </is>
@@ -11068,14 +10984,14 @@
           <t>237,200</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>[사이다툰 모음집] "너...혹시 뭐 돼?" 날 무시하는 사람들 참교육썰 모음집ㅣ코기툰ㅣ영상툰ㅣ썰툰ㅣ사연툰ㅣ고민툰ㅣ사이다툰ㅣ개그썰ㅣ일상툰</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>와우사연</t>
         </is>
@@ -11115,14 +11031,14 @@
           <t>111,500</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>재벌가 맏며느리에 "고졸이라 무식한데, 눈치도 없어!" 모욕한 시어머니, 미국 재벌회장과 2조원 계약을 살린, MIT 나온 국제회계사가 바로 며느리?..| 노후사연 | 인생사연 |</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>개구리 영상툰</t>
         </is>
@@ -11162,14 +11078,14 @@
           <t>64,900</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>(사이다툰) 시월드에서 받은 서러움 시원하게 갚아줬습니다😈 모음집🌈ㅣ영상툰ㅣ썰툰 [개구리툰]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>AI 스튜디오 황혼</t>
         </is>
@@ -11209,14 +11125,14 @@
           <t>14,035</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>“동서는 우리 가족 아니잖아!” 칠순잔치에서 작은 며느리를 모욕한 맏며느리의 최후 #시니어드라마 #감동드라마</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>442사람사는이야기</t>
         </is>
@@ -11256,14 +11172,14 @@
           <t>777</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>[오늘의사연] 형부부가 세상을 떠나자 아내가 조카를 데려오자는데 30년이 지나고 그선택의 결과가 드러나는데.. 라디오드라마 사연읽어주는남자 442</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>이주은 부부가족상담센터</t>
         </is>
@@ -11303,14 +11219,14 @@
           <t>4,530</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>고부갈등으로 손주 맡기고 이혼한 며느리 ㅣ 이주은 부부상담</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>월하야담</t>
         </is>
@@ -11350,14 +11266,14 @@
           <t>28,980</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>김치를 빨랫줄에 널어놓는 며느리를 모두가 비웃었지만, 그 줄을 본 어사가 충격에 말을 잃은 이유 |야담 | 옛날이야기 | 민담 | 수면동화 | 오디오북| 전설| 설화</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>사연많은 박여사</t>
         </is>
@@ -11397,14 +11313,14 @@
           <t>55,900</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>📮[풀영상] 남편 몰래 준비한 9년의 결말!</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>부부해결사 정다원</t>
         </is>
@@ -11444,14 +11360,14 @@
           <t>9,040</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>이 질문법으로, 배우자 성격을 한번에 알 수 있습니다</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>사연있네</t>
         </is>
@@ -11491,14 +11407,14 @@
           <t>9,170</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>“형님도 노래 한 곡 해보세요” 망신 주려던 재벌가 둘째 며느리, 첫째 며느리가 마이크를 잡자 그룹 파티가 조용해졌습니다</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>야담민담</t>
         </is>
@@ -11538,14 +11454,14 @@
           <t>187</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>난감하네! 볼 것, 못볼 것, 다 봐버린 시아버지와 며느리,</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>조용한 눈물</t>
         </is>
@@ -11585,14 +11501,14 @@
           <t>246</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>♥뇌졸중으로 쓰러진 아내 3년 후 남편 인생이 완전히 뒤집혔다#감동사연 #노후사연 #사연라디오 #부부갈등 #가족갈등 #재산분할 #사이다결말 #반전사연  #60대공감 #70대공감</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>어쩌다마주친사연</t>
         </is>
@@ -11632,14 +11548,14 @@
           <t>5,320</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>(톡툰) 불륜 사실 들통나 저와 이혼한 와이프가 스스로 목숨을 끊었다는데, 처남은 장례식에 와달라네요</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>사람과 세상</t>
         </is>
@@ -11679,14 +11595,14 @@
           <t>32,400</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>시골에 혼자 사는 노모의 전기요금이 매달 90만 원씩 나오자, 딸이 원인을 찾으려고 집안 차단기를 내렸다. 그런데 그 순간, 담장 너머에서 “사람 살려!”라는 비명이 터졌다!</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>시니어본색</t>
         </is>
@@ -11726,14 +11642,14 @@
           <t>62</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>시댁 눈치 끝! 명절마다 터지는 진짜 속마음 폭로</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>오늘의사연</t>
         </is>
@@ -11773,14 +11689,14 @@
           <t>17,860</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>"오늘부로 며느리 안 합니다!"가난한 며느리 시어머니 생신상 뒤집어 엎고 나왔습니다</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>인생저편</t>
         </is>
@@ -11820,14 +11736,14 @@
           <t>1,465</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>"오늘부로 이 집안 종노릇, 은퇴합니다! "시아버지 팔순상 뒤집어엎고 나온 반찬가게 며느리의 충격 정체...ㅣ노후사연ㅣ반전사연ㅣ감동사연ㅣ오디오북</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>토마톡툰</t>
         </is>
@@ -11867,14 +11783,14 @@
           <t>49,900</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>내가 결혼에 목메는 줄 알고 자기 집에만 결혼예단 해달라고 하는 예비신랑에게 시원하게 파혼 통보.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>위로같은이야기</t>
         </is>
@@ -11914,14 +11830,14 @@
           <t>66,917</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>가난한 첫째 아들 큰 며느리 식모처럼 무시하던 시어머니와 시댁 식구들의 최후...ㅣ인생사연ㅣ감동사연ㅣ사연라디오ㅣ사연 오디오북</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>🔥황혼인생🔥</t>
         </is>
@@ -11961,14 +11877,14 @@
           <t>440</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>"동서도 성악 한번 해봐!" 성악 출신 큰며느리가 비웃었는데, 첫 소절을 부르자 객석이 얼어붙었습니다.  #5060 #6070 #7080 #참교육사연 #반전사연 #사이다사연</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>사연극장</t>
         </is>
@@ -12008,14 +11924,14 @@
           <t>822</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>학창 시절 나를 왕따시킨 일진이 며느리 엄마 "방 빼세요" 한마디에 결혼식장 뒤집어진 역대급 참교육 시니어사연l사이다사연l사연라디오l오디오북</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>은빛펀치</t>
         </is>
@@ -12055,14 +11971,14 @@
           <t>3,218</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>30년 만에 만난 동창이 내 머리에 물을 부은 충격적인 이유#동창회#여자친구#시니어사연#사연</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>사연맘</t>
         </is>
@@ -12102,14 +12018,14 @@
           <t>1,881</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>60대 여성이 털어놓은 속사정, 젊은 남편의 예기치 못한 행동에 분노 폭발하다 | 인생조언 오디오북 사연 노후</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>톡툰한입</t>
         </is>
@@ -12149,14 +12065,14 @@
           <t>15,060</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>강남 아파트 해온 동서는 상전, 반반 결혼한 나는 종년? "해온 거 없으면 일하는 게 룰이야" 그 룰대로 남편 인생 지옥 보내줬습니다</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>사연의문</t>
         </is>
@@ -12196,14 +12112,14 @@
           <t>3,928</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>지하철 입구에서 1,000원 김밥을 사주던 가난한 여고생, 어느 날 학교 정문에 벤츠 10대가 멈춰 섰다|노후사연|감동사연|사연라디오|오디오북|시니어사연|</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>봉자 카페</t>
         </is>
@@ -12243,14 +12159,14 @@
           <t>9,094</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>우리 부모님 생신 상 안 차릴 거면 이혼해</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>며느리의 눈물</t>
         </is>
@@ -12290,14 +12206,14 @@
           <t>164</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>결혼식도 없이 재벌가 며느리가 된 나… 사랑 없는 결혼의 끝에서 기적이 시작됐다</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>우주아빠멋대로</t>
         </is>
@@ -12337,14 +12253,14 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>바람난 와이프 친구들과 파티장 에서 몰래 탄 정체불명 액체 난 그걸 내연남 칵테일과 바꿔버렸습니다| 시니어사연 | 감동사연 | 오디오북 | 인생사연 | 노후사연 | 라디오사연</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>시월드</t>
         </is>
@@ -12384,14 +12300,14 @@
           <t>6,660</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>두 며느리 시험하려 청소부 변장한 시어머니, 며느리의 충격적 반응에 참교육한 사연인생사연|감동사연|노후사연|시니어사연l사이다사연l고부갈등</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>마음쉼터</t>
         </is>
@@ -12431,14 +12347,14 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>친정아빠 49재 다녀왔더니 남편은 이혼서류 남기고 해외여행 갔길래 저는 제 명의 집을 팔았습니다 며칠뒤, 시모의 다급한 전화 59통 “왜 우리집 현관 비밀번호가 틀리냐!”</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>며느리 사연</t>
         </is>
@@ -12478,14 +12394,14 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>“친정 가면 돌아오지 마” 아버지 기일에 절 내쫓은 남편… 저는 그날로 결혼까지 끝냈습니다</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>LuciaHarrington MarieDalton</t>
         </is>
@@ -12525,14 +12441,14 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>실화사연  몰래 회사에서 불륜을 즐기던 아내 차에서 발견한 충격증거ㅣ라디오드라마ㅣ사이다사연ㅣ</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>며느리의 사연</t>
         </is>
@@ -12572,14 +12488,14 @@
           <t>30</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>기러기생활 5년 성공한후 이혼하자는 아내, '나이스' 외치며 도장 찍었습니다</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>인생의조각들</t>
         </is>
@@ -12619,14 +12535,14 @@
           <t>338</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>신청사연 퇴근길 한 노인을 구하다 찢어진 양복을 세탁소에 맡겼더니 걸려온 전화에 세탁소 갔더니 사장님이 명함을 들고 떨고있는데 감동사연사이다사연라디오드라마사연라디오</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>사연 아리랑</t>
         </is>
@@ -12666,14 +12582,14 @@
           <t>54</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>40년 희생한 아내에게 이혼 서류 던진 남편, 15년 숨겨온 추악한 진실에 엄마는 무너졌습니다</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>사이다인생사연</t>
         </is>
@@ -12713,14 +12629,14 @@
           <t>1,125</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>상견례 날 무시당한 시골 할머니… 손자의 한마디에 재벌가가 침묵했다/감동사연/시니어사연/노후이야기/오디오북</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>이야기 천국</t>
         </is>
@@ -12760,14 +12676,14 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>" 52세 아들과같이 살았습니다... 그런데 내가 쓰러지고 나서야 알았습니다."</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>인생썰 극장</t>
         </is>
@@ -12807,14 +12723,14 @@
           <t>53</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>아들 집 사는 데 전 재산을 보탰습니다… 그런데 제 방은 없었습니다 | [노후 사연극] EP.1</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>24시 사연방</t>
         </is>
@@ -12854,14 +12770,14 @@
           <t>87</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>산악회 갔다가 불륜 버스 탔습니다. 등산 모임인줄 알고 가입했다가 경찰까지 오고...</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>xiexiemei</t>
         </is>
@@ -12901,14 +12817,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>죄송하지만, YouTube 링크의 내용을 확인할 수 없습니다. 해당 내용에 대한 요약이나 특정 내용을 말씀해 주시면, 그에 맞춰 같은 의미의 문장을 만들어 드리겠습니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Ila Jaxen</t>
         </is>
@@ -12948,14 +12864,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>(실화사연) 시아버님 아래서 뽀얀게 흘러나오길래 시원하게 빼줬어요... [라디오드라마][사이다사연]</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>인생사연 TV</t>
         </is>
@@ -12995,14 +12911,14 @@
           <t>32</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>삼촌에게 한겨울에 쫓겨난 고아, 20년뒤에 스타 건축가로 나타나는데!!! 12살 소년의 인생 역전 이야기</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">추억의 향기 </t>
         </is>
@@ -13042,7 +12958,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>72세 어머니, 사위와 딸이 노인 요양시설 알아보길래 조용히 집과 전재산 들고 사라지는데     시니어사연   오디오북   노후인생   가족갈등</t>
         </is>
